--- a/public/UbicacionesVallasV2.xlsx
+++ b/public/UbicacionesVallasV2.xlsx
@@ -3634,7 +3634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
@@ -3653,7 +3653,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="18" style="1" width="10.7"/>
   </cols>
   <sheetData>
@@ -3719,7 +3720,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -3779,7 +3780,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -3839,7 +3840,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -3899,7 +3900,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -3959,7 +3960,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -4019,7 +4020,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -4079,7 +4080,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
@@ -4139,7 +4140,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -4199,7 +4200,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -4259,7 +4260,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -4319,7 +4320,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
@@ -4379,7 +4380,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -4439,7 +4440,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -4499,7 +4500,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -4559,7 +4560,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -4619,7 +4620,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
@@ -4679,7 +4680,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -4739,7 +4740,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>56</v>
       </c>
@@ -4797,7 +4798,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
@@ -4857,7 +4858,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
@@ -4917,7 +4918,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -4977,7 +4978,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -5037,7 +5038,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
@@ -5097,7 +5098,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>17</v>
       </c>
@@ -5157,7 +5158,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>17</v>
       </c>
@@ -5217,7 +5218,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
@@ -5277,7 +5278,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>56</v>
       </c>
@@ -5337,7 +5338,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -5397,7 +5398,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>56</v>
       </c>
@@ -5457,7 +5458,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
         <v>56</v>
       </c>
@@ -5517,7 +5518,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
         <v>17</v>
       </c>
@@ -5577,7 +5578,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>17</v>
       </c>
@@ -5637,7 +5638,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>17</v>
       </c>
@@ -5697,7 +5698,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
@@ -5757,7 +5758,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>187</v>
       </c>
@@ -5813,7 +5814,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>56</v>
       </c>
@@ -5873,7 +5874,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -5933,7 +5934,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
         <v>17</v>
       </c>
@@ -5993,7 +5994,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
         <v>187</v>
       </c>
@@ -6053,7 +6054,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>56</v>
       </c>
@@ -6113,7 +6114,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
         <v>56</v>
       </c>
@@ -6171,7 +6172,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
         <v>56</v>
       </c>
@@ -6233,7 +6234,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
         <v>56</v>
       </c>
@@ -6293,7 +6294,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
         <v>17</v>
       </c>
@@ -6353,7 +6354,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
         <v>17</v>
       </c>
@@ -6413,7 +6414,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
         <v>56</v>
       </c>
@@ -6475,7 +6476,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
         <v>17</v>
       </c>
@@ -6535,7 +6536,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
         <v>17</v>
       </c>
@@ -6595,7 +6596,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
         <v>17</v>
       </c>
@@ -6655,7 +6656,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
@@ -6715,7 +6716,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
         <v>17</v>
       </c>
@@ -6775,7 +6776,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
         <v>17</v>
       </c>
@@ -6835,7 +6836,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
         <v>17</v>
       </c>
@@ -6895,7 +6896,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
         <v>17</v>
       </c>
@@ -6955,7 +6956,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
         <v>17</v>
       </c>
@@ -7015,7 +7016,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
         <v>17</v>
       </c>
@@ -7075,7 +7076,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
         <v>17</v>
       </c>
@@ -7135,7 +7136,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
         <v>17</v>
       </c>
@@ -7195,7 +7196,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
         <v>17</v>
       </c>
@@ -7255,7 +7256,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
         <v>17</v>
       </c>
@@ -7315,7 +7316,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
         <v>56</v>
       </c>
@@ -7375,7 +7376,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
         <v>17</v>
       </c>
@@ -7431,7 +7432,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
         <v>17</v>
       </c>
@@ -7487,7 +7488,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>17</v>
       </c>
@@ -7545,7 +7546,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
         <v>17</v>
       </c>
@@ -7603,7 +7604,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
         <v>17</v>
       </c>
@@ -7661,7 +7662,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
         <v>17</v>
       </c>
@@ -7719,7 +7720,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
         <v>56</v>
       </c>
@@ -7775,7 +7776,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
         <v>56</v>
       </c>
@@ -7835,7 +7836,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
         <v>17</v>
       </c>
@@ -7897,7 +7898,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
         <v>17</v>
       </c>
@@ -7957,7 +7958,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
         <v>17</v>
       </c>
@@ -8019,7 +8020,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
         <v>17</v>
       </c>
@@ -8079,7 +8080,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
         <v>17</v>
       </c>
@@ -8141,7 +8142,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
         <v>17</v>
       </c>
@@ -8203,7 +8204,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
         <v>17</v>
       </c>
@@ -8265,7 +8266,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
         <v>17</v>
       </c>
@@ -8325,7 +8326,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
         <v>17</v>
       </c>
@@ -8387,7 +8388,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
         <v>17</v>
       </c>
@@ -8447,7 +8448,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
         <v>17</v>
       </c>
@@ -8503,7 +8504,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
         <v>17</v>
       </c>
@@ -8559,7 +8560,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
         <v>17</v>
       </c>
@@ -8615,7 +8616,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
         <v>17</v>
       </c>
@@ -8671,7 +8672,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
         <v>17</v>
       </c>
@@ -8727,7 +8728,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
         <v>17</v>
       </c>
@@ -8783,7 +8784,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
         <v>17</v>
       </c>
@@ -8839,7 +8840,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
         <v>17</v>
       </c>
@@ -8895,7 +8896,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
         <v>17</v>
       </c>
@@ -8949,7 +8950,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
         <v>17</v>
       </c>
@@ -9003,7 +9004,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
         <v>17</v>
       </c>
@@ -9057,7 +9058,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
         <v>17</v>
       </c>
@@ -9113,7 +9114,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
         <v>17</v>
       </c>
@@ -9169,7 +9170,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
         <v>17</v>
       </c>
@@ -9225,7 +9226,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
         <v>17</v>
       </c>
@@ -9281,7 +9282,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
         <v>17</v>
       </c>
@@ -9335,7 +9336,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
         <v>17</v>
       </c>
@@ -9391,7 +9392,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
         <v>17</v>
       </c>
@@ -9447,7 +9448,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
         <v>17</v>
       </c>
@@ -9503,7 +9504,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
         <v>17</v>
       </c>
@@ -9559,7 +9560,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
         <v>17</v>
       </c>
@@ -9615,7 +9616,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
         <v>17</v>
       </c>
@@ -9671,7 +9672,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
         <v>17</v>
       </c>
@@ -9727,7 +9728,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="16" t="s">
         <v>486</v>
       </c>
@@ -9781,7 +9782,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="16" t="s">
         <v>492</v>
       </c>
@@ -9837,7 +9838,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="16" t="s">
         <v>17</v>
       </c>
@@ -9893,7 +9894,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="16" t="s">
         <v>17</v>
       </c>
@@ -9947,7 +9948,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="16" t="s">
         <v>56</v>
       </c>
@@ -10001,7 +10002,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="16" t="s">
         <v>17</v>
       </c>
@@ -10057,7 +10058,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="16" t="s">
         <v>187</v>
       </c>
@@ -10113,7 +10114,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="16" t="s">
         <v>519</v>
       </c>
@@ -10165,7 +10166,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="16" t="s">
         <v>525</v>
       </c>
@@ -10219,7 +10220,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="16" t="s">
         <v>56</v>
       </c>
@@ -10273,7 +10274,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="16" t="s">
         <v>17</v>
       </c>
@@ -10329,7 +10330,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="16" t="s">
         <v>17</v>
       </c>
@@ -10385,7 +10386,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="16" t="s">
         <v>56</v>
       </c>
@@ -10441,7 +10442,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="16" t="s">
         <v>17</v>
       </c>
@@ -10495,7 +10496,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="16" t="s">
         <v>56</v>
       </c>
@@ -10547,7 +10548,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="16" t="s">
         <v>17</v>
       </c>
@@ -10601,7 +10602,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="16" t="s">
         <v>56</v>
       </c>
@@ -10655,7 +10656,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="16" t="s">
         <v>56</v>
       </c>
@@ -10709,7 +10710,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="16" t="s">
         <v>187</v>
       </c>
@@ -10761,7 +10762,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="16" t="s">
         <v>56</v>
       </c>
@@ -10813,7 +10814,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="16" t="s">
         <v>56</v>
       </c>
@@ -10865,7 +10866,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="16" t="s">
         <v>56</v>
       </c>
@@ -10917,7 +10918,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="16" t="s">
         <v>525</v>
       </c>
@@ -10967,7 +10968,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="16" t="s">
         <v>56</v>
       </c>
@@ -11019,7 +11020,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="16" t="s">
         <v>56</v>
       </c>
@@ -11069,7 +11070,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="16" t="s">
         <v>17</v>
       </c>
@@ -11121,7 +11122,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="16" t="s">
         <v>17</v>
       </c>
@@ -11173,7 +11174,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="16" t="s">
         <v>17</v>
       </c>
@@ -11225,7 +11226,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="16" t="s">
         <v>17</v>
       </c>
@@ -11277,7 +11278,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="16" t="s">
         <v>56</v>
       </c>
@@ -11327,7 +11328,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="16" t="s">
         <v>17</v>
       </c>
@@ -11379,7 +11380,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="16" t="s">
         <v>17</v>
       </c>
@@ -11431,7 +11432,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="16" t="s">
         <v>56</v>
       </c>
@@ -11485,7 +11486,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="16" t="s">
         <v>17</v>
       </c>
@@ -11537,7 +11538,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="16" t="s">
         <v>17</v>
       </c>
@@ -11693,7 +11694,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="16" t="s">
         <v>56</v>
       </c>
@@ -11745,7 +11746,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="16" t="s">
         <v>56</v>
       </c>
@@ -11797,7 +11798,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="16" t="s">
         <v>17</v>
       </c>
@@ -11849,7 +11850,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="16" t="s">
         <v>17</v>
       </c>
@@ -11901,7 +11902,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="16" t="s">
         <v>17</v>
       </c>
@@ -11955,7 +11956,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="16" t="s">
         <v>670</v>
       </c>
@@ -12005,7 +12006,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="16" t="s">
         <v>17</v>
       </c>
@@ -12059,7 +12060,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="16" t="s">
         <v>17</v>
       </c>
@@ -12113,7 +12114,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="16" t="s">
         <v>56</v>
       </c>
@@ -12167,7 +12168,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="16" t="s">
         <v>56</v>
       </c>
@@ -12217,7 +12218,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="16" t="s">
         <v>56</v>
       </c>
@@ -12267,7 +12268,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="16" t="s">
         <v>56</v>
       </c>
@@ -12317,7 +12318,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="16" t="s">
         <v>17</v>
       </c>
@@ -12373,7 +12374,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="16" t="s">
         <v>17</v>
       </c>
@@ -12429,7 +12430,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="16" t="s">
         <v>56</v>
       </c>
@@ -12485,7 +12486,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="16" t="s">
         <v>56</v>
       </c>
@@ -12541,7 +12542,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="16" t="s">
         <v>17</v>
       </c>
@@ -12597,7 +12598,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="16" t="s">
         <v>525</v>
       </c>
@@ -12651,7 +12652,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="16" t="s">
         <v>525</v>
       </c>
@@ -12705,7 +12706,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="16" t="s">
         <v>17</v>
       </c>
@@ -12761,7 +12762,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="16" t="s">
         <v>17</v>
       </c>
@@ -12817,7 +12818,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="16" t="s">
         <v>741</v>
       </c>
@@ -12871,7 +12872,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="16" t="s">
         <v>56</v>
       </c>
@@ -12927,7 +12928,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="16" t="s">
         <v>525</v>
       </c>
@@ -12981,7 +12982,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="16" t="s">
         <v>56</v>
       </c>
@@ -13037,7 +13038,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="16" t="s">
         <v>56</v>
       </c>
@@ -13093,7 +13094,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="16" t="s">
         <v>17</v>
       </c>
@@ -13147,7 +13148,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="16" t="s">
         <v>17</v>
       </c>
@@ -13203,7 +13204,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="16" t="s">
         <v>56</v>
       </c>
@@ -13259,7 +13260,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="16" t="s">
         <v>17</v>
       </c>
@@ -13315,7 +13316,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="16" t="s">
         <v>17</v>
       </c>
@@ -13371,7 +13372,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="16" t="s">
         <v>56</v>
       </c>
@@ -13425,7 +13426,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="16" t="s">
         <v>56</v>
       </c>
@@ -13479,7 +13480,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="16" t="s">
         <v>56</v>
       </c>
@@ -13533,7 +13534,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="16" t="s">
         <v>56</v>
       </c>
@@ -13589,7 +13590,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="16" t="s">
         <v>56</v>
       </c>
@@ -13643,7 +13644,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="16" t="s">
         <v>17</v>
       </c>
@@ -13699,7 +13700,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="16" t="s">
         <v>17</v>
       </c>
@@ -13755,7 +13756,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="16" t="s">
         <v>17</v>
       </c>
@@ -13811,7 +13812,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="16" t="s">
         <v>17</v>
       </c>
@@ -13867,7 +13868,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="16" t="s">
         <v>56</v>
       </c>
@@ -13923,7 +13924,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="16" t="s">
         <v>56</v>
       </c>
@@ -13979,7 +13980,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="16" t="s">
         <v>525</v>
       </c>
@@ -14035,7 +14036,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="16" t="s">
         <v>56</v>
       </c>
@@ -14091,7 +14092,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="16" t="s">
         <v>56</v>
       </c>
@@ -14147,7 +14148,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="16" t="s">
         <v>17</v>
       </c>
@@ -14203,7 +14204,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="16" t="s">
         <v>17</v>
       </c>
@@ -14259,7 +14260,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="16" t="s">
         <v>17</v>
       </c>
@@ -14315,7 +14316,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="16" t="s">
         <v>17</v>
       </c>
@@ -14371,7 +14372,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="16" t="s">
         <v>17</v>
       </c>
@@ -14427,7 +14428,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="16" t="s">
         <v>17</v>
       </c>
@@ -14483,7 +14484,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="16" t="s">
         <v>17</v>
       </c>
@@ -14539,7 +14540,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="16" t="s">
         <v>17</v>
       </c>
@@ -14595,7 +14596,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="16" t="s">
         <v>17</v>
       </c>
@@ -14651,7 +14652,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="16" t="s">
         <v>17</v>
       </c>
@@ -14707,7 +14708,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="16" t="s">
         <v>56</v>
       </c>
@@ -14763,7 +14764,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="16" t="s">
         <v>56</v>
       </c>
@@ -14817,7 +14818,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="16" t="s">
         <v>17</v>
       </c>
@@ -14873,7 +14874,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="16" t="s">
         <v>525</v>
       </c>
@@ -14927,7 +14928,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="16" t="s">
         <v>56</v>
       </c>
@@ -14981,7 +14982,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="16" t="s">
         <v>56</v>
       </c>
@@ -15035,7 +15036,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="16" t="s">
         <v>17</v>
       </c>
@@ -15091,7 +15092,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="16" t="s">
         <v>17</v>
       </c>
@@ -15147,7 +15148,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="16" t="s">
         <v>17</v>
       </c>
@@ -15203,7 +15204,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="16" t="s">
         <v>17</v>
       </c>
@@ -15259,7 +15260,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="16" t="s">
         <v>17</v>
       </c>
@@ -15315,7 +15316,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="16" t="s">
         <v>56</v>
       </c>
@@ -15369,7 +15370,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="16" t="s">
         <v>17</v>
       </c>
@@ -15425,7 +15426,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="16" t="s">
         <v>17</v>
       </c>
@@ -15481,7 +15482,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="16" t="s">
         <v>17</v>
       </c>
@@ -15539,7 +15540,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="16" t="s">
         <v>17</v>
       </c>
@@ -15597,7 +15598,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="16" t="s">
         <v>17</v>
       </c>
@@ -15653,7 +15654,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="16" t="s">
         <v>17</v>
       </c>
@@ -15709,7 +15710,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="16" t="s">
         <v>56</v>
       </c>
@@ -15763,7 +15764,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="16" t="s">
         <v>56</v>
       </c>
@@ -15817,7 +15818,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="16" t="s">
         <v>56</v>
       </c>
@@ -15873,7 +15874,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="16" t="s">
         <v>56</v>
       </c>
@@ -15927,7 +15928,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="16" t="s">
         <v>56</v>
       </c>
@@ -15983,7 +15984,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="16" t="s">
         <v>56</v>
       </c>
@@ -16039,7 +16040,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="16" t="s">
         <v>17</v>
       </c>
@@ -16093,7 +16094,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="16" t="s">
         <v>17</v>
       </c>
@@ -16145,7 +16146,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="3"/>
     </row>
-    <row r="222" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="16" t="s">
         <v>187</v>
       </c>
@@ -16197,7 +16198,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="3"/>
     </row>
-    <row r="223" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="16" t="s">
         <v>56</v>
       </c>
@@ -16253,7 +16254,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="3"/>
     </row>
-    <row r="224" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="16" t="s">
         <v>56</v>
       </c>
@@ -16309,7 +16310,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
     </row>
-    <row r="225" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="16" t="s">
         <v>17</v>
       </c>
@@ -16363,7 +16364,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="3"/>
     </row>
-    <row r="226" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="16" t="s">
         <v>17</v>
       </c>
@@ -16417,7 +16418,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="3"/>
     </row>
-    <row r="227" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="16" t="s">
         <v>17</v>
       </c>
@@ -16471,7 +16472,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="3"/>
     </row>
-    <row r="228" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="16" t="s">
         <v>187</v>
       </c>
@@ -16525,7 +16526,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="3"/>
     </row>
-    <row r="229" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="16" t="s">
         <v>17</v>
       </c>
@@ -16577,7 +16578,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
     </row>
-    <row r="230" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="16" t="s">
         <v>17</v>
       </c>
@@ -16629,7 +16630,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="3"/>
     </row>
-    <row r="231" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="16" t="s">
         <v>17</v>
       </c>
@@ -16681,7 +16682,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="3"/>
     </row>
-    <row r="232" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="16" t="s">
         <v>17</v>
       </c>
@@ -16733,7 +16734,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
     </row>
-    <row r="233" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="16" t="s">
         <v>17</v>
       </c>
@@ -16785,7 +16786,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
     </row>
-    <row r="234" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="16" t="s">
         <v>17</v>
       </c>
@@ -16839,7 +16840,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
     </row>
-    <row r="235" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="16" t="s">
         <v>17</v>
       </c>
@@ -16893,7 +16894,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="3"/>
     </row>
-    <row r="236" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="16" t="s">
         <v>17</v>
       </c>
@@ -16947,7 +16948,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="3"/>
     </row>
-    <row r="237" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="16" t="s">
         <v>17</v>
       </c>
@@ -16999,7 +17000,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="3"/>
     </row>
-    <row r="238" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="16" t="s">
         <v>17</v>
       </c>
@@ -17051,7 +17052,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="3"/>
     </row>
-    <row r="239" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="16" t="s">
         <v>17</v>
       </c>
@@ -17103,7 +17104,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="3"/>
     </row>
-    <row r="240" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="16" t="s">
         <v>17</v>
       </c>
@@ -17157,7 +17158,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="3"/>
     </row>
-    <row r="241" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="16" t="s">
         <v>17</v>
       </c>
@@ -17211,7 +17212,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="3"/>
     </row>
-    <row r="242" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="16" t="s">
         <v>17</v>
       </c>
@@ -17265,7 +17266,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
     </row>
-    <row r="243" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="16" t="s">
         <v>17</v>
       </c>
@@ -17319,7 +17320,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="3"/>
     </row>
-    <row r="244" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="16" t="s">
         <v>17</v>
       </c>
@@ -17373,7 +17374,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="3"/>
     </row>
-    <row r="245" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="16" t="s">
         <v>17</v>
       </c>
@@ -17427,7 +17428,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
     </row>
-    <row r="246" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="16" t="s">
         <v>17</v>
       </c>
@@ -38594,14 +38595,7 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q246">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="San Pablo De Tiquina"/>
-        <filter val="San Pablo De Tiquina -"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q246"/>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" display="https://maps.app.goo.gl/eg1cMcUP1zrxFe6h9"/>
     <hyperlink ref="L37" r:id="rId2" display="https://maps.app.goo.gl/QUgqpH1fcNoEYXdq5"/>

--- a/public/UbicacionesVallasV2.xlsx
+++ b/public/UbicacionesVallasV2.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3209" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3222" uniqueCount="1106">
   <si>
     <t xml:space="preserve">TIPO DE ESTRUCTURA</t>
   </si>
@@ -3320,6 +3320,27 @@
   </si>
   <si>
     <t xml:space="preserve">-16.5250278,-68.1482222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGITAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente a la Corte de Justicia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cara mira hacia Av. 6  de agosto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6X3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maps.app.goo.gl/bMv5qfn8qt6rVf4y9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.835596, -64.903506</t>
   </si>
 </sst>
 </file>
@@ -3650,7 +3671,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="25.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="33.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.9"/>
@@ -17483,23 +17504,51 @@
       <c r="Z246" s="3"/>
     </row>
     <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="3"/>
-      <c r="B247" s="3"/>
-      <c r="C247" s="3"/>
-      <c r="D247" s="3"/>
-      <c r="E247" s="3"/>
-      <c r="F247" s="3"/>
-      <c r="G247" s="3"/>
-      <c r="H247" s="3"/>
-      <c r="I247" s="3"/>
-      <c r="J247" s="3"/>
-      <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
-      <c r="M247" s="3"/>
-      <c r="N247" s="3"/>
-      <c r="O247" s="3"/>
-      <c r="P247" s="3"/>
-      <c r="Q247" s="3"/>
+      <c r="A247" s="16" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="D247" s="16" t="s">
+        <v>975</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F247" s="14" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H247" s="14"/>
+      <c r="I247" s="16" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J247" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K247" s="17" t="n">
+        <v>6200</v>
+      </c>
+      <c r="L247" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="M247" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="N247" s="5"/>
+      <c r="O247" s="15"/>
+      <c r="P247" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q247" s="9" t="s">
+        <v>416</v>
+      </c>
       <c r="R247" s="3"/>
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>

--- a/public/UbicacionesVallasV2.xlsx
+++ b/public/UbicacionesVallasV2.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet3" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet3!$A$1:$Q$246</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet3!$A$1:$Q$247</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -38720,7 +38720,7 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q246"/>
+  <autoFilter ref="A1:Q247"/>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" display="https://maps.app.goo.gl/eg1cMcUP1zrxFe6h9"/>
     <hyperlink ref="L37" r:id="rId2" display="https://maps.app.goo.gl/QUgqpH1fcNoEYXdq5"/>
